--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\Logic mo\fuzzy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452D6A62-6ED6-466A-BB0B-FF12768E3291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FCF66C8-6340-4C1B-8987-F95F262755AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{37CD2175-D9AC-47C9-BD75-0046D7BEF046}"/>
   </bookViews>
@@ -498,6 +498,9 @@
       <c r="C3" t="s">
         <v>0</v>
       </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
       <c r="J3" s="1"/>
       <c r="K3" t="s">
         <v>7</v>
@@ -522,6 +525,9 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
+      <c r="I5">
+        <v>1</v>
+      </c>
       <c r="J5" s="2"/>
       <c r="K5" t="s">
         <v>8</v>
@@ -542,6 +548,9 @@
       <c r="E7" s="5"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
+      <c r="I7">
+        <v>0</v>
+      </c>
       <c r="J7" s="3"/>
       <c r="K7" t="s">
         <v>9</v>
@@ -569,14 +578,14 @@
         <v>2</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="F11" s="6"/>
       <c r="G11" s="6"/>
     </row>
     <row r="12" spans="3:11" x14ac:dyDescent="0.35">
       <c r="D12" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="7"/>
     </row>
@@ -610,14 +619,14 @@
         <v>2</v>
       </c>
       <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
+      <c r="F17" s="7"/>
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D18" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E18" s="6"/>
+      <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
     </row>
